--- a/data/trans_camb/P32B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P32B-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 14,15</t>
+          <t>4,1; 14,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 10,69</t>
+          <t>1,06; 10,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 6,66</t>
+          <t>-2,04; 6,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 2,9</t>
+          <t>-7,39; 2,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 6,61</t>
+          <t>-4,75; 6,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 0,0</t>
+          <t>-10,15; 0,18</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 8,8</t>
+          <t>1,42; 8,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 8,27</t>
+          <t>0,83; 7,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 3,5</t>
+          <t>-2,93; 3,74</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,41; 1933,99</t>
+          <t>82,6; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 1457,05</t>
+          <t>0,22; 1499,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,83; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 805,33</t>
+          <t>19,18; 829,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 852,29</t>
+          <t>5,0; 866,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-94,81; 431,36</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 4,12</t>
+          <t>-1,31; 4,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,43</t>
+          <t>-4,09; -0,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,03</t>
+          <t>-2,48; 4,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,57</t>
+          <t>-1,12; 2,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,34</t>
+          <t>-2,94; -0,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,14</t>
+          <t>-1,99; 2,29</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,17; 855,37</t>
+          <t>-63,78; 766,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,19; 637,76</t>
+          <t>-62,41; 684,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,53</t>
+          <t>1,97; 7,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,93</t>
+          <t>0,49; 5,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,07</t>
+          <t>1,8; 5,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,94</t>
+          <t>-3,27; 0,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 1,5</t>
+          <t>-2,92; 1,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,39</t>
+          <t>-2,69; 1,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-4,47; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 0,0</t>
+          <t>-4,64; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,16</t>
+          <t>-3,21; 1,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,32</t>
+          <t>-2,7; 0,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,66</t>
+          <t>-2,45; 0,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 0,93</t>
+          <t>-2,41; 0,97</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-90,73; 312,35</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 7,78</t>
+          <t>-0,24; 8,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 7,92</t>
+          <t>-0,07; 8,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,0</t>
+          <t>-4,73; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 5,09</t>
+          <t>-0,05; 5,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 6,0</t>
+          <t>-0,31; 5,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,68</t>
+          <t>-1,25; 4,53</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 1,13</t>
+          <t>-3,57; 1,14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 3,53</t>
+          <t>-2,13; 3,54</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,37</t>
+          <t>-1,8; 3,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,66; -0,84</t>
+          <t>-7,13; -0,84</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,36; 0,92</t>
+          <t>-6,28; 0,94</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 3,49</t>
+          <t>-4,75; 2,96</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,0</t>
+          <t>-3,78; 0,07</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,7</t>
+          <t>-2,6; 1,93</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,58</t>
+          <t>-1,89; 2,7</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-85,44; 314,22</t>
+          <t>-86,72; 301,37</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-73,02; 434,97</t>
+          <t>-68,91; 373,5</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,56</t>
+          <t>1,99; 6,49</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,09</t>
+          <t>1,69; 5,79</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,35</t>
+          <t>0,99; 4,27</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,01</t>
+          <t>0,44; 3,9</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,29</t>
+          <t>0,8; 4,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,66</t>
+          <t>0,16; 4,59</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,99</t>
+          <t>1,8; 4,9</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,7</t>
+          <t>1,66; 4,46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,64</t>
+          <t>0,71; 3,67</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,35</t>
+          <t>0,58; 3,42</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,51</t>
+          <t>-0,07; 2,39</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,2</t>
+          <t>-0,25; 2,25</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,58</t>
+          <t>-2,5; 0,94</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,39</t>
+          <t>-3,33; -0,38</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,08</t>
+          <t>-1,95; 3,16</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,1</t>
+          <t>-0,08; 2,07</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,16</t>
+          <t>-0,69; 1,16</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,79</t>
+          <t>-0,45; 1,77</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>22,39; —</t>
+          <t>8,92; —</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-34,07; 779,9</t>
+          <t>-35,82; 737,86</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-80,0; 483,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-63,8; 709,73</t>
+          <t>-65,19; 578,43</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,86</t>
+          <t>1,2; 3,04</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,09</t>
+          <t>0,51; 2,12</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,13</t>
+          <t>0,33; 2,17</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,4</t>
+          <t>-1,23; 0,44</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,83</t>
+          <t>-0,92; 0,86</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,39</t>
+          <t>-0,82; 1,36</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,96</t>
+          <t>0,59; 1,88</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,4</t>
+          <t>0,23; 1,42</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,57</t>
+          <t>0,08; 1,54</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>91,38; 537,71</t>
+          <t>92,96; 543,63</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>40,23; 377,81</t>
+          <t>38,4; 393,79</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>21,08; 381,53</t>
+          <t>20,03; 366,01</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 79,7</t>
+          <t>-78,24; 100,15</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-63,65; 154,89</t>
+          <t>-61,33; 169,78</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 231,18</t>
+          <t>-52,38; 214,67</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>46,47; 284,25</t>
+          <t>48,87; 288,83</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>17,34; 215,81</t>
+          <t>16,6; 224,96</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5,11; 233,72</t>
+          <t>5,96; 229,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32B-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P32B-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-2,46</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,18</t>
+          <t>-0,54</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,1; 14,31</t>
+          <t>3,56; 14,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,55</t>
+          <t>0,98; 10,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 6,34</t>
+          <t>-2,87; 4,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 2,81</t>
+          <t>-7,29; 2,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 6,65</t>
+          <t>-4,56; 6,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 0,18</t>
+          <t>-10,05; 0,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,68</t>
+          <t>1,15; 8,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,94</t>
+          <t>0,52; 7,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 3,74</t>
+          <t>-2,92; 2,11</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-93,83%</t>
+          <t>-82,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-7,67%</t>
+          <t>-23,37%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>82,6; —</t>
+          <t>49,91; 1777,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1499,73</t>
+          <t>-2,8; 1608,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-88,83; —</t>
+          <t>-97,72; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,18; 829,97</t>
+          <t>17,91; 1044,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,0; 866,31</t>
+          <t>0,33; 809,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,81; 431,36</t>
+          <t>-86,4; 373,98</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,41</t>
+          <t>-0,5</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,02</t>
+          <t>-1,12; 4,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,44</t>
+          <t>-3,97; -0,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 4,11</t>
+          <t>-2,8; 3,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -923,17 +923,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,78</t>
+          <t>-1,15; 2,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; -0,3</t>
+          <t>-3,26; -0,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,29</t>
+          <t>-1,93; 2,01</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-25,36%</t>
+          <t>-32,46%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-32,6%</t>
+          <t>-39,65%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-63,78; 766,53</t>
+          <t>-59,12; 779,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,41; 684,47</t>
+          <t>-62,69; 546,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,24</t>
+          <t>5,25</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>4,18</t>
         </is>
       </c>
     </row>
@@ -1114,17 +1114,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,89</t>
+          <t>2,72; 9,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 5,41</t>
+          <t>0,47; 4,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,94</t>
+          <t>2,45; 7,04</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-0,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,58</t>
+          <t>-3,34; 0,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,52</t>
+          <t>-3,06; 1,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1,34</t>
+          <t>-3,09; 0,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,0</t>
+          <t>-4,5; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,0</t>
+          <t>-3,61; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,19</t>
+          <t>-3,22; 1,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,11</t>
+          <t>-2,69; 0,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,61</t>
+          <t>-2,42; 0,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 0,97</t>
+          <t>-2,48; 0,67</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-38,13%</t>
+          <t>-47,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-18,99%</t>
+          <t>-21,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-34,14%</t>
+          <t>-40,88%</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,96; 258,65</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,42</t>
         </is>
       </c>
     </row>
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 8,08</t>
+          <t>-0,22; 7,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 8,43</t>
+          <t>-0,79; 8,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,0</t>
+          <t>-4,84; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 5,82</t>
+          <t>-0,07; 5,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 5,79</t>
+          <t>-0,4; 6,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 4,53</t>
+          <t>-1,24; 4,22</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 1,14</t>
+          <t>-3,96; 1,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 3,54</t>
+          <t>-2,22; 3,13</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,5</t>
+          <t>-2,36; 3,2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -0,84</t>
+          <t>-7,09; -0,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 0,94</t>
+          <t>-6,16; 0,91</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 2,96</t>
+          <t>-4,7; 3,21</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,07</t>
+          <t>-3,51; 0,13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,93</t>
+          <t>-2,41; 1,97</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,7</t>
+          <t>-2,03; 2,64</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-14,5%</t>
+          <t>-15,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-86,72; 301,37</t>
+          <t>-85,82; 305,55</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-68,91; 373,5</t>
+          <t>-68,78; 542,75</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,11</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>3,64</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,49</t>
+          <t>2,04; 6,34</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,79</t>
+          <t>1,69; 5,98</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,27</t>
+          <t>1,67; 6,66</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,9</t>
+          <t>0,44; 4,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,86</t>
+          <t>0,84; 5,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,59</t>
+          <t>1,66; 8,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,9</t>
+          <t>1,75; 4,98</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,46</t>
+          <t>1,8; 4,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,67</t>
+          <t>2,22; 5,84</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,42</t>
+          <t>0,53; 3,11</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,39</t>
+          <t>-0,09; 2,51</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,25</t>
+          <t>-0,21; 2,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,94</t>
+          <t>-2,55; 0,6</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-3,33; -0,38</t>
+          <t>-3,35; -0,39</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,16</t>
+          <t>-2,06; 2,78</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,07</t>
+          <t>-0,13; 2,01</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,16</t>
+          <t>-0,6; 1,07</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,77</t>
+          <t>-0,54; 1,71</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>177,12%</t>
+          <t>169,21%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>62,86%</t>
         </is>
       </c>
     </row>
@@ -2295,12 +2295,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>8,92; —</t>
+          <t>20,24; —</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-35,82; 737,86</t>
+          <t>-26,14; 667,38</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,3; 463,62</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-65,19; 578,43</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,18</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,04</t>
+          <t>1,21; 3,07</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,12</t>
+          <t>0,59; 2,14</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,17</t>
+          <t>0,58; 2,37</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,44</t>
+          <t>-1,33; 0,43</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,86</t>
+          <t>-0,9; 0,86</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,36</t>
+          <t>-0,21; 2,18</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,88</t>
+          <t>0,54; 1,89</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,42</t>
+          <t>0,29; 1,4</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,54</t>
+          <t>0,54; 2,02</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>140,34%</t>
+          <t>165,45%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>132,93%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>92,96; 543,63</t>
+          <t>101,96; 595,01</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>38,4; 393,79</t>
+          <t>50,35; 435,98</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>20,03; 366,01</t>
+          <t>37,56; 446,91</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-78,24; 100,15</t>
+          <t>-79,42; 105,04</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-61,33; 169,78</t>
+          <t>-59,05; 180,05</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 214,67</t>
+          <t>-21,99; 358,46</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>48,87; 288,83</t>
+          <t>38,84; 276,78</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>16,6; 224,96</t>
+          <t>20,33; 213,81</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>5,96; 229,3</t>
+          <t>43,76; 311,91</t>
         </is>
       </c>
     </row>
